--- a/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 4.xlsx
+++ b/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 4.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24729"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\1. For Youtube\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Penjualan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7397E29-A1F6-4A7A-9BC9-1A61D2CFC839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="11070"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -129,7 +128,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
@@ -282,13 +281,38 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -304,32 +328,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -614,7 +613,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:N24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -634,22 +633,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="2:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
     </row>
     <row r="3" spans="2:14" s="8" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
@@ -690,10 +689,16 @@
       <c r="E4" s="11">
         <v>1799000</v>
       </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="13"/>
+      <c r="F4" s="31">
+        <f>IF(D4="A",10%,IF(D4="B",5%,IF(D4="C",15%)))</f>
+        <v>0.1</v>
+      </c>
+      <c r="G4" s="13">
+        <f>E4-(E4*F4)</f>
+        <v>1619100</v>
+      </c>
       <c r="H4" s="4"/>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -710,16 +715,22 @@
       <c r="E5" s="11">
         <v>1499000</v>
       </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13"/>
-      <c r="I5" s="23" t="s">
+      <c r="F5" s="31">
+        <f t="shared" ref="F5:F11" si="0">IF(D5="A",10%,IF(D5="B",5%,IF(D5="C",15%)))</f>
+        <v>0.15</v>
+      </c>
+      <c r="G5" s="13">
+        <f t="shared" ref="G5:G11" si="1">E5-(E5*F5)</f>
+        <v>1274150</v>
+      </c>
+      <c r="I5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="9">
@@ -734,14 +745,20 @@
       <c r="E6" s="11">
         <v>429000</v>
       </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="13"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
+      <c r="F6" s="31">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="G6" s="13">
+        <f t="shared" si="1"/>
+        <v>407550</v>
+      </c>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="9">
@@ -756,16 +773,22 @@
       <c r="E7" s="11">
         <v>699000</v>
       </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="13"/>
-      <c r="I7" s="26" t="s">
+      <c r="F7" s="31">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="G7" s="13">
+        <f t="shared" si="1"/>
+        <v>664050</v>
+      </c>
+      <c r="I7" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="27"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="9">
@@ -780,16 +803,22 @@
       <c r="E8" s="11">
         <v>699000</v>
       </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="13"/>
-      <c r="I8" s="26" t="s">
+      <c r="F8" s="31">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="G8" s="13">
+        <f t="shared" si="1"/>
+        <v>664050</v>
+      </c>
+      <c r="I8" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
     </row>
     <row r="9" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="9">
@@ -804,16 +833,22 @@
       <c r="E9" s="11">
         <v>278000</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="13"/>
-      <c r="I9" s="26" t="s">
+      <c r="F9" s="31">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="13">
+        <f t="shared" si="1"/>
+        <v>250200</v>
+      </c>
+      <c r="I9" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="9">
@@ -828,16 +863,22 @@
       <c r="E10" s="11">
         <v>700000</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="13"/>
-      <c r="I10" s="28" t="s">
+      <c r="F10" s="31">
+        <f t="shared" si="0"/>
+        <v>0.15</v>
+      </c>
+      <c r="G10" s="13">
+        <f t="shared" si="1"/>
+        <v>595000</v>
+      </c>
+      <c r="I10" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-      <c r="M10" s="28"/>
-      <c r="N10" s="28"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="9">
@@ -852,99 +893,123 @@
       <c r="E11" s="11">
         <v>1299000</v>
       </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="13"/>
-      <c r="I11" s="24" t="s">
+      <c r="F11" s="31">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="G11" s="13">
+        <f t="shared" si="1"/>
+        <v>1169100</v>
+      </c>
+      <c r="I11" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="15"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="14">
+        <f>MAX(G4:G11)</f>
+        <v>1619100</v>
+      </c>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="14"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="13">
+        <f>MIN(G4:G11)</f>
+        <v>250200</v>
+      </c>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="14"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="13">
+        <f>AVERAGE(G4:G11)</f>
+        <v>830400</v>
+      </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="13"/>
-      <c r="I15" s="30" t="s">
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="12">
+        <f>COUNTIF(D4:D11,"A")</f>
+        <v>3</v>
+      </c>
+      <c r="I15" s="16" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="13"/>
-      <c r="I16" s="31" t="s">
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="12">
+        <f>COUNTIF(D4:D11,"B")</f>
+        <v>3</v>
+      </c>
+      <c r="I16" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="J16" s="29"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="29"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="13"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="12">
+        <f>COUNTIF(D4:D11,"C")</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="2"/>
@@ -984,6 +1049,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B1:G2"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="I5:N6"/>
     <mergeCell ref="I11:N13"/>
     <mergeCell ref="B16:F16"/>
@@ -993,14 +1063,9 @@
     <mergeCell ref="I9:N9"/>
     <mergeCell ref="I10:N10"/>
     <mergeCell ref="I16:N16"/>
-    <mergeCell ref="B1:G2"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="I16" r:id="rId1" xr:uid="{35D0D974-58A0-4F3D-BCC7-A6E3541DD867}"/>
+    <hyperlink ref="I16" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 4.xlsx
+++ b/exercise/Admin/Admin Penjualan/Tes Excel Admin Penjualan 4.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24729"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Penjualan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\1. For Youtube\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7397E29-A1F6-4A7A-9BC9-1A61D2CFC839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="11070"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -128,7 +129,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
@@ -281,11 +282,31 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -295,9 +316,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -307,28 +325,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -613,7 +614,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:N24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -633,22 +634,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="2:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
     </row>
     <row r="3" spans="2:14" s="8" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
@@ -689,16 +690,10 @@
       <c r="E4" s="11">
         <v>1799000</v>
       </c>
-      <c r="F4" s="31">
-        <f>IF(D4="A",10%,IF(D4="B",5%,IF(D4="C",15%)))</f>
-        <v>0.1</v>
-      </c>
-      <c r="G4" s="13">
-        <f>E4-(E4*F4)</f>
-        <v>1619100</v>
-      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="16" t="s">
         <v>30</v>
       </c>
     </row>
@@ -715,22 +710,16 @@
       <c r="E5" s="11">
         <v>1499000</v>
       </c>
-      <c r="F5" s="31">
-        <f t="shared" ref="F5:F11" si="0">IF(D5="A",10%,IF(D5="B",5%,IF(D5="C",15%)))</f>
-        <v>0.15</v>
-      </c>
-      <c r="G5" s="13">
-        <f t="shared" ref="G5:G11" si="1">E5-(E5*F5)</f>
-        <v>1274150</v>
-      </c>
-      <c r="I5" s="17" t="s">
+      <c r="F5" s="12"/>
+      <c r="G5" s="13"/>
+      <c r="I5" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="9">
@@ -745,20 +734,14 @@
       <c r="E6" s="11">
         <v>429000</v>
       </c>
-      <c r="F6" s="31">
-        <f t="shared" si="0"/>
-        <v>0.05</v>
-      </c>
-      <c r="G6" s="13">
-        <f t="shared" si="1"/>
-        <v>407550</v>
-      </c>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="13"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="9">
@@ -773,22 +756,16 @@
       <c r="E7" s="11">
         <v>699000</v>
       </c>
-      <c r="F7" s="31">
-        <f t="shared" si="0"/>
-        <v>0.05</v>
-      </c>
-      <c r="G7" s="13">
-        <f t="shared" si="1"/>
-        <v>664050</v>
-      </c>
-      <c r="I7" s="21" t="s">
+      <c r="F7" s="12"/>
+      <c r="G7" s="13"/>
+      <c r="I7" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="9">
@@ -803,22 +780,16 @@
       <c r="E8" s="11">
         <v>699000</v>
       </c>
-      <c r="F8" s="31">
-        <f t="shared" si="0"/>
-        <v>0.05</v>
-      </c>
-      <c r="G8" s="13">
-        <f t="shared" si="1"/>
-        <v>664050</v>
-      </c>
-      <c r="I8" s="21" t="s">
+      <c r="F8" s="12"/>
+      <c r="G8" s="13"/>
+      <c r="I8" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
     </row>
     <row r="9" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="9">
@@ -833,22 +804,16 @@
       <c r="E9" s="11">
         <v>278000</v>
       </c>
-      <c r="F9" s="31">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-      <c r="G9" s="13">
-        <f t="shared" si="1"/>
-        <v>250200</v>
-      </c>
-      <c r="I9" s="21" t="s">
+      <c r="F9" s="12"/>
+      <c r="G9" s="13"/>
+      <c r="I9" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="9">
@@ -863,22 +828,16 @@
       <c r="E10" s="11">
         <v>700000</v>
       </c>
-      <c r="F10" s="31">
-        <f t="shared" si="0"/>
-        <v>0.15</v>
-      </c>
-      <c r="G10" s="13">
-        <f t="shared" si="1"/>
-        <v>595000</v>
-      </c>
-      <c r="I10" s="23" t="s">
+      <c r="F10" s="12"/>
+      <c r="G10" s="13"/>
+      <c r="I10" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="9">
@@ -893,123 +852,99 @@
       <c r="E11" s="11">
         <v>1299000</v>
       </c>
-      <c r="F11" s="31">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-      <c r="G11" s="13">
-        <f t="shared" si="1"/>
-        <v>1169100</v>
-      </c>
-      <c r="I11" s="18" t="s">
+      <c r="F11" s="12"/>
+      <c r="G11" s="13"/>
+      <c r="I11" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="14">
-        <f>MAX(G4:G11)</f>
-        <v>1619100</v>
-      </c>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="15"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="13">
-        <f>MIN(G4:G11)</f>
-        <v>250200</v>
-      </c>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="14"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="13">
-        <f>AVERAGE(G4:G11)</f>
-        <v>830400</v>
-      </c>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="14"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="12">
-        <f>COUNTIF(D4:D11,"A")</f>
-        <v>3</v>
-      </c>
-      <c r="I15" s="16" t="s">
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="13"/>
+      <c r="I15" s="30" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="12">
-        <f>COUNTIF(D4:D11,"B")</f>
-        <v>3</v>
-      </c>
-      <c r="I16" s="24" t="s">
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="13"/>
+      <c r="I16" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="12">
-        <f>COUNTIF(D4:D11,"C")</f>
-        <v>2</v>
-      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="13"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="2"/>
@@ -1049,11 +984,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B1:G2"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
     <mergeCell ref="I5:N6"/>
     <mergeCell ref="I11:N13"/>
     <mergeCell ref="B16:F16"/>
@@ -1063,9 +993,14 @@
     <mergeCell ref="I9:N9"/>
     <mergeCell ref="I10:N10"/>
     <mergeCell ref="I16:N16"/>
+    <mergeCell ref="B1:G2"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="I16" r:id="rId1"/>
+    <hyperlink ref="I16" r:id="rId1" xr:uid="{35D0D974-58A0-4F3D-BCC7-A6E3541DD867}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
